--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -12,6 +12,7 @@
     <sheet name="CAN_intrarregional" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Exportaciones_bilaterales" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CAN_destinos_2023" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="EFTA_destinos_2023" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73701,4 +73702,130 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Destino de las exportaciones de mercancías de los miembros del EFTA en 2023 (% del total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fuente: WITS (Banco Mundial) a partir de UN Comtrade; UE = suma de los 27 Estados miembros. Cálculo propio (Code/datos_comercio.py); datos brutos por socio en Code/datos/destinos.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Exportador</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EFTA (resto de miembros)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EE. UU.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UE-27</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Resto del mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="E7" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -73562,7 +73562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73607,7 +73607,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto del mundo (sin Reino Unido)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -73630,7 +73635,10 @@
         <v>5.93</v>
       </c>
       <c r="F5" t="n">
-        <v>64.48</v>
+        <v>63.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="6">
@@ -73652,7 +73660,10 @@
         <v>13.7</v>
       </c>
       <c r="F6" t="n">
-        <v>46.4</v>
+        <v>45.49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="7">
@@ -73674,7 +73685,10 @@
         <v>13.63</v>
       </c>
       <c r="F7" t="n">
-        <v>38.62</v>
+        <v>37.72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="8">
@@ -73696,7 +73710,10 @@
         <v>10.6</v>
       </c>
       <c r="F8" t="n">
-        <v>35.25</v>
+        <v>33.26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>
@@ -73710,7 +73727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73755,7 +73772,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto del mundo (sin Reino Unido)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -73778,7 +73800,10 @@
         <v>63.11</v>
       </c>
       <c r="F5" t="n">
-        <v>18.47</v>
+        <v>9.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -73800,7 +73825,10 @@
         <v>67.16</v>
       </c>
       <c r="F6" t="n">
-        <v>26.76</v>
+        <v>7.72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.04</v>
       </c>
     </row>
     <row r="7">
@@ -73822,7 +73850,10 @@
         <v>39.52</v>
       </c>
       <c r="F7" t="n">
-        <v>34.55</v>
+        <v>31.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,31 +1459,196 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Noruega</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Islandia</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Suiza</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Exportaciones a Reino Unido / totales: Noruega</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Referéndum de Islandia sobre reanudar la negociación con la UE: votos en contra</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>LIGA.net (2026)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://news.liga.net/en/world/news/iceland-voted-against-resuming-eu-accession-negotiations-in-a-referendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Tasa de seguridad de Ecuador sobre importaciones colombianas (inicial)</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C39" t="n">
         <v>30</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E39" t="n">
         <v>2026</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Portafolio (2026)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.portafolio.co/negocios/comercio/de-30-a-50-la-cronologia-de-la-guerra-comercial-que-enfrenta-a-colombia-y-ecuador-489248</t>
         </is>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Exportaciones_bilaterales" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CAN_destinos_2023" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EFTA_destinos_2023" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NAFTA_vehiculos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74024,4 +74025,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Producción de vehículos de motor en Norteamérica (unidades) y reglas de origen del automóvil</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fuente: OICA (1999: tabla de producción de 1999; 2024: OICA vía statbase.org); reglas: texto del USMCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EE. UU.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cuota de México (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B5" t="n">
+        <v>13024978</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3058813</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1549925</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17633716</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10522394</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1339288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4202724</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16064406</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regla de origen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NAFTA (%)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USMCA (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Contenido regional (turismos)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Contenido laboral (&gt;= 16 USD/h)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Acero y aluminio de la región</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -14,6 +14,7 @@
     <sheet name="CAN_destinos_2023" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EFTA_destinos_2023" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="NAFTA_vehiculos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="USA_importaciones" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74181,4 +74182,569 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Importaciones de mercancías de USA por origen (millones de dólares corrientes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fuente: WITS (Banco Mundial) a partir de UN Comtrade, indicador MPRT-TRD-VL (importaciones declaradas por el importador). Cálculo propio (Code/datos_comercio.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Total (WLD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B5" t="n">
+        <v>50333.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>131916.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>41345.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>689029.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B6" t="n">
+        <v>62745.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>148277.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48505.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>770821.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74108.10000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>159691.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54396.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>817627.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87119.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>171330.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>65811.60000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>898025.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96074.60000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>177916.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75094.89999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>944350.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111067.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>201433.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87775.10000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1059220.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>135923.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>230816.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100012.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1217933</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>131334.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>216234.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>102267.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1140900.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B13" t="n">
+        <v>136025.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>212398.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133510.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1200095.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B14" t="n">
+        <v>139686.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>225035.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>163313.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1302833.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B15" t="n">
+        <v>157881.9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>260161.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>210500.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1525304.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B16" t="n">
+        <v>172388.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>294382.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>259836</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1734849.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B17" t="n">
+        <v>200499.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>307723.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>305778.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1918997.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B18" t="n">
+        <v>212878</v>
+      </c>
+      <c r="C18" t="n">
+        <v>317481.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>340106.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2017120.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B19" t="n">
+        <v>218066.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>339074.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>356304.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2164834</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B20" t="n">
+        <v>178321.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>227577.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>309530.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1601895.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B21" t="n">
+        <v>232251.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>280426.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>382964.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1968259.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B22" t="n">
+        <v>265113.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>317921.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>417340.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2263619.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B23" t="n">
+        <v>279957.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>327502.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>444386</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2334677.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B24" t="n">
+        <v>283133.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>337126.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>459107.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2326590.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B25" t="n">
+        <v>296855.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>354171.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>486296.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2410855.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B26" t="n">
+        <v>299181.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>301942.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>504028.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2313424.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B27" t="n">
+        <v>296199.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>282919.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>481310.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2247167.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B28" t="n">
+        <v>315733.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>305647.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>525764.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2405276.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B29" t="n">
+        <v>349195.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>325683.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>563203.1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2611432.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B30" t="n">
+        <v>361320.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>326628.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>472464.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2567492.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B31" t="n">
+        <v>328861.8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>276195.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>457164.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2405381.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B32" t="n">
+        <v>388357.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>363904.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>541531.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2932976.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B33" t="n">
+        <v>459177.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>446623.9</v>
+      </c>
+      <c r="D33" t="n">
+        <v>575688.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3372902.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B34" t="n">
+        <v>480050.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>429604.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>448017.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3168471.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,16 +1462,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>NAFTA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exportaciones a la UE-27 / totales: Noruega</t>
+          <t>Exportaciones intrarregionales / totales</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>67.2</v>
+        <v>35.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1479,32 +1479,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2023</v>
+        <v>1981</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+          <t>Cálculo propio con UN Comtrade (hoja NAFTA_intrarregional)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://wits.worldbank.org</t>
+          <t>https://comtradeapi.un.org</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>NAFTA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exportaciones a la UE-27 / totales: Islandia</t>
+          <t>Exportaciones intrarregionales / totales</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>63.1</v>
+        <v>41</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1512,32 +1512,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2023</v>
+        <v>1989</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+          <t>Cálculo propio con UN Comtrade (hoja NAFTA_intrarregional)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://wits.worldbank.org</t>
+          <t>https://comtradeapi.un.org</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>NAFTA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Exportaciones a la UE-27 / totales: Suiza</t>
+          <t>Exportaciones intrarregionales / totales</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39.5</v>
+        <v>48.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1545,32 +1545,32 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+          <t>Cálculo propio con UN Comtrade (hoja NAFTA_intrarregional)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://wits.worldbank.org</t>
+          <t>https://comtradeapi.un.org</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>NAFTA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exportaciones a Reino Unido / totales: Noruega</t>
+          <t>Exportaciones intrarregionales / totales (máximo)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>19</v>
+        <v>56.1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1578,11 +1578,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+          <t>Cálculo propio con WITS (hoja NAFTA_intrarregional)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1594,16 +1594,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>NAFTA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Referéndum de Islandia sobre reanudar la negociación con la UE: votos en contra</t>
+          <t>Exportaciones intrarregionales / totales</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>52.8</v>
+        <v>48</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1611,47 +1611,643 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LIGA.net (2026)</t>
+          <t>Cálculo propio con WITS (hoja NAFTA_intrarregional)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://news.liga.net/en/world/news/iceland-voted-against-resuming-eu-accession-negotiations-in-a-referendum</t>
+          <t>https://wits.worldbank.org</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Exportaciones intrarregionales / totales</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja NAFTA_intrarregional)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Exportaciones de México a EE. UU. / totales</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>80</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja Exportaciones_bilaterales)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Exportaciones de Canadá a EE. UU. / totales</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Exportaciones de EE. UU. a Canadá / totales</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Exportaciones de EE. UU. a México / totales</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Importaciones de EE. UU. desde México</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>480.1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>miles de millones USD</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>WITS (hoja USA_importaciones)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Importaciones de EE. UU. desde China</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>448</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>miles de millones USD</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>WITS (hoja USA_importaciones)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Importaciones de EE. UU. desde Canadá</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>miles de millones USD</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>WITS (hoja USA_importaciones)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cuota de México en la producción de vehículos de Norteamérica</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OICA (hoja NAFTA_vehiculos)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.oica.net/category/production-statistics/1999-statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cuota de México en la producción de vehículos de Norteamérica</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OICA vía statbase.org (hoja NAFTA_vehiculos)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://statbase.org/datasets/road-transportation/motor-vehicle-production/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Efecto del NAFTA en el bienestar de México / EE. UU. / Canadá</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1,31 / 0,08 / -0,06</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Caliendo y Parro (2015)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.nber.org/papers/w18508</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NAFTA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Efecto estimado del USMCA en el PIB real de EE. UU.</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>USITC (2019)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.usitc.gov/press_room/news_release/2019/er0418ll1087.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Exportaciones intrarregionales / totales (Islandia, Noruega y Suiza)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (destinos.csv)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Noruega</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Islandia</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Exportaciones a la UE-27 / totales: Suiza</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Exportaciones a Reino Unido / totales: Noruega</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Cálculo propio con WITS (hoja EFTA_destinos_2023)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://wits.worldbank.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Referéndum de Islandia sobre reanudar la negociación con la UE: votos en contra</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>LIGA.net (2026)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://news.liga.net/en/world/news/iceland-voted-against-resuming-eu-accession-negotiations-in-a-referendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Tasa de seguridad de Ecuador sobre importaciones colombianas (inicial)</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C57" t="n">
         <v>30</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E57" t="n">
         <v>2026</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Portafolio (2026)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.portafolio.co/negocios/comercio/de-30-a-50-la-cronologia-de-la-guerra-comercial-que-enfrenta-a-colombia-y-ecuador-489248</t>
         </is>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos_3B35.xlsx
@@ -16,6 +16,7 @@
     <sheet name="USA_importaciones" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="NAFTA_intrarregional" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Exportaciones_bilaterales" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MERCOSUR_destinos_2023" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2258,6 +2259,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Destino de las exportaciones de mercancías de los miembros del MERCOSUR en 2023 (% del total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fuente: WITS (Banco Mundial) a partir de UN Comtrade; UE = suma de los 27 Estados miembros. Cálculo propio (Code/datos_comercio.py); datos brutos por socio en Code/datos/destinos.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Exportador</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MERCOSUR (resto de miembros)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EE. UU.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UE-27</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Resto del mundo (sin Reino Unido)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
